--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260215.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20260215.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,258 @@
         <v>141.98</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>102708283KT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spice - Ginger (Ground)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>72.98999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10200118</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spice - Crushed Red Pepper</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22.49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10207579</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Salt - Sea Coarse</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="E5" t="n">
+        <v>71.28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>24510105CB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Box Cake - 10x10x5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="E6" t="n">
+        <v>124.98</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>409ML91005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Choc Curls - Dark</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>302.49</v>
+      </c>
+      <c r="E7" t="n">
+        <v>302.49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>433SLINERBL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - Silicone Coated</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>153.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2458GCC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cake Circle - 8" (Gold)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>155.96</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>24510GCC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cake Circle - 10" (Gold)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E10" t="n">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>245CCGR1914</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/2 Sheet</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="E11" t="n">
+        <v>79.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>150BB6218N</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bag Paper - 6.5x17.75 Window</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>150.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>588URN1001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Urnex - Brewer Cleaner</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>93.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
